--- a/artfynd/A 59248-2019 artfynd.xlsx
+++ b/artfynd/A 59248-2019 artfynd.xlsx
@@ -1747,7 +1747,7 @@
         <v>121067017</v>
       </c>
       <c r="B12" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 59248-2019 artfynd.xlsx
+++ b/artfynd/A 59248-2019 artfynd.xlsx
@@ -1747,7 +1747,7 @@
         <v>121067017</v>
       </c>
       <c r="B12" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
